--- a/tools/importer/reports/import-career.report.xlsx
+++ b/tools/importer/reports/import-career.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-07T23:14:23.555Z</t>
+    <t>2026-09-08T10:16:17.163Z</t>
   </si>
   <si>
     <t>Homepage | AUMOVIO</t>
@@ -73,7 +73,7 @@
     <t>career</t>
   </si>
   <si>
-    <t>2026-09-08T01:00:11.166Z</t>
+    <t>2026-09-08T10:24:48.465Z</t>
   </si>
   <si>
     <t>Career | AUMOVIO</t>
@@ -91,7 +91,7 @@
     <t>en/company</t>
   </si>
   <si>
-    <t>2026-09-08T01:00:17.140Z</t>
+    <t>2026-09-08T10:24:52.694Z</t>
   </si>
   <si>
     <t>Company | AUMOVIO</t>
@@ -109,7 +109,7 @@
     <t>en/solutions</t>
   </si>
   <si>
-    <t>2026-09-08T01:00:22.074Z</t>
+    <t>2026-09-08T10:24:57.700Z</t>
   </si>
   <si>
     <t>Solutions | AUMOVIO</t>

--- a/tools/importer/reports/import-career.report.xlsx
+++ b/tools/importer/reports/import-career.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-08T10:16:17.163Z</t>
+    <t>2026-09-08T14:42:10.268Z</t>
   </si>
   <si>
     <t>Homepage | AUMOVIO</t>
@@ -73,7 +73,7 @@
     <t>career</t>
   </si>
   <si>
-    <t>2026-09-08T10:24:48.465Z</t>
+    <t>2026-09-08T14:42:17.519Z</t>
   </si>
   <si>
     <t>Career | AUMOVIO</t>
@@ -91,7 +91,7 @@
     <t>en/company</t>
   </si>
   <si>
-    <t>2026-09-08T10:24:52.694Z</t>
+    <t>2026-09-08T14:42:23.589Z</t>
   </si>
   <si>
     <t>Company | AUMOVIO</t>
@@ -109,7 +109,7 @@
     <t>en/solutions</t>
   </si>
   <si>
-    <t>2026-09-08T10:24:57.700Z</t>
+    <t>2026-09-08T14:42:29.381Z</t>
   </si>
   <si>
     <t>Solutions | AUMOVIO</t>
